--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>١‏/١٠‏/٢٠٢٦، ٤:١٩:٤١ ص</v>
+        <v>١‏/١٠‏/٢٠٢٦، ٩:٢٨:٢٠ م</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.7.0</v>
+        <v>6.7.2</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>١‏/١٠‏/٢٠٢٦، ٩:٢٨:٢٠ م</v>
+        <v>١‏/١٠‏/٢٠٢٦، ١٠:٠٢:٤٧ م</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.7.2</v>
+        <v>6.8.0</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>١‏/١٠‏/٢٠٢٦، ١٠:٠٢:٤٧ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٨:٥٩:٤١ ص</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.8.0</v>
+        <v>6.9.0</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٠:١٦:٤٢ ص</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١١:٠٠:١٠ ص</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.1</v>
+        <v>6.9.3</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١١:٠٠:١٠ ص</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١١:٢٩:٥٤ ص</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.3</v>
+        <v>6.9.4</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١١:٢٩:٥٤ ص</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٠٣:٢٩ م</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.4</v>
+        <v>6.9.5</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٠٣:٢٩ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٢٨:٠٣ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٢٨:٠٣ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٥٨:٠٣ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٥٨:٠٣ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١:١٨:٣٦ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١:١٨:٣٦ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٢:٥١:٣٠ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٢:٥١:٣٠ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٣:٣٥:١٦ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٣:٣٥:١٦ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٣:٥٠:٠٢ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٣:٥٠:٠٢ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٥:٥٤:٠٥ م</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.5</v>
+        <v>6.9.13</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٥:٥٤:٠٥ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٦:٣١:١٧ م</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.13</v>
+        <v>6.9.14</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٦:٣١:١٧ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٧:١٧:٥٩ م</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.14</v>
+        <v>6.9.15</v>
       </c>
     </row>
   </sheetData>

--- a/source/tests/output/formats.xlsx
+++ b/source/tests/output/formats.xlsx
@@ -477,7 +477,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٧:١٧:٥٩ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٧:٤٩:١٧ م</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.15</v>
+        <v>6.9.16</v>
       </c>
     </row>
   </sheetData>
